--- a/jpbsCVdata/cv_data_with_aboutme.xlsx
+++ b/jpbsCVdata/cv_data_with_aboutme.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" firstSheet="0" activeTab="8"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,11 +25,14 @@
     <sheet name="AboutMe" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="633">
   <si>
     <t>Section</t>
   </si>
@@ -1371,12 +1374,18 @@
     <t>organization</t>
   </si>
   <si>
+    <t>service_type</t>
+  </si>
+  <si>
     <t xml:space="preserve">Associate Editor</t>
   </si>
   <si>
     <t xml:space="preserve">Journal of International Financial Markets, Institutions and Money</t>
   </si>
   <si>
+    <t>Academic</t>
+  </si>
+  <si>
     <t>2008-01</t>
   </si>
   <si>
@@ -1447,6 +1456,9 @@
   </si>
   <si>
     <t xml:space="preserve">Professional Risk Managers International Association</t>
+  </si>
+  <si>
+    <t>Professional</t>
   </si>
   <si>
     <t>2018-01</t>
@@ -1889,77 +1901,76 @@
     ;</t>
   </si>
   <si>
-    <t xml:space="preserve">section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">full_about</t>
+    <t>section</t>
+  </si>
+  <si>
+    <t>content</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>full_about</t>
   </si>
   <si>
     <t xml:space="preserve">I am a Finance Professor with over 25 years of extensive domestic and international experience in online and traditional academic program management. I create academic programs and courses that monetize academic effort and yield institutional revenue enhancement and stakeholder success. I maintain real-world relevance through being a Financial Professional Designation Exam Trainer, Financial Risk Management Specialist, Financial Market Consultant, Expert on Big Data, Implementer of Natural Language Processing, Artificial Intelligence and Machine Learning applications in Finance.</t>
   </si>
   <si>
-    <t xml:space="preserve">short_about</t>
+    <t>short_about</t>
   </si>
   <si>
     <t xml:space="preserve">Finance Professor with 25+ years of experience in academic program management, specializing in online education, enrollment growth, and revenue generation.</t>
   </si>
   <si>
-    <t xml:space="preserve">tagline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">leadership_philosophy</t>
+    <t>tagline</t>
+  </si>
+  <si>
+    <t>leadership_philosophy</t>
   </si>
   <si>
     <t xml:space="preserve">I build programs that serve students, faculty, and institutions simultaneously—creating sustainable growth through strategic vision, operational excellence, and authentic stakeholder engagement.</t>
   </si>
   <si>
-    <t xml:space="preserve">email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">john.broussard@rutgers.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tinyurl.com/c3wdneyp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">linkedin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tinyurl.com/5bfex8hv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orcid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0000-0002-5090-9947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">location</t>
+    <t>email</t>
+  </si>
+  <si>
+    <t>john.broussard@rutgers.edu</t>
+  </si>
+  <si>
+    <t>website</t>
+  </si>
+  <si>
+    <t>tinyurl.com/c3wdneyp</t>
+  </si>
+  <si>
+    <t>linkedin</t>
+  </si>
+  <si>
+    <t>tinyurl.com/5bfex8hv</t>
+  </si>
+  <si>
+    <t>orcid</t>
+  </si>
+  <si>
+    <t>0000-0002-5090-9947</t>
+  </si>
+  <si>
+    <t>location</t>
   </si>
   <si>
     <t xml:space="preserve">Oklahoma City, Oklahoma, USA</t>
   </si>
   <si>
-    <t xml:space="preserve">phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
+    <t>phone</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3">
     <font>
       <sz val="11.000000"/>
@@ -1968,11 +1979,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-      <b/>
     </font>
     <font>
       <sz val="11.000000"/>
@@ -1990,22 +2001,23 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="4">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="17" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2018,6 +2030,289 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2241,13 +2536,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -2282,19 +2576,20 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -2320,7 +2615,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -2332,7 +2627,7 @@
       <c r="D2" t="s">
         <v>342</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>2016</v>
       </c>
       <c r="F2" t="s">
@@ -2340,7 +2635,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -2352,7 +2647,7 @@
       <c r="D3" t="s">
         <v>346</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>2009</v>
       </c>
       <c r="F3" t="s">
@@ -2360,7 +2655,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -2372,7 +2667,7 @@
       <c r="D4" t="s">
         <v>349</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>2003</v>
       </c>
       <c r="F4" t="s">
@@ -2380,7 +2675,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -2392,7 +2687,7 @@
       <c r="D5" t="s">
         <v>352</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>2002</v>
       </c>
       <c r="F5" t="s">
@@ -2400,7 +2695,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -2412,7 +2707,7 @@
       <c r="D6" t="s">
         <v>355</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>2002</v>
       </c>
       <c r="F6" t="s">
@@ -2420,7 +2715,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -2432,7 +2727,7 @@
       <c r="D7" t="s">
         <v>357</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>2001</v>
       </c>
       <c r="F7" t="s">
@@ -2440,7 +2735,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -2452,7 +2747,7 @@
       <c r="D8" t="s">
         <v>359</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>2000</v>
       </c>
       <c r="F8" t="s">
@@ -2460,7 +2755,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -2472,7 +2767,7 @@
       <c r="D9" t="s">
         <v>362</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>1995</v>
       </c>
       <c r="F9" t="s">
@@ -2480,7 +2775,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -2492,7 +2787,7 @@
       <c r="D10" t="s">
         <v>365</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1994</v>
       </c>
       <c r="F10" t="s">
@@ -2500,19 +2795,20 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -2544,7 +2840,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -2562,7 +2858,7 @@
       <c r="G2" t="s">
         <v>370</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2" t="b">
@@ -2570,7 +2866,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -2588,7 +2884,7 @@
       <c r="G3" t="s">
         <v>370</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" t="b">
@@ -2596,7 +2892,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -2614,7 +2910,7 @@
       <c r="G4" t="s">
         <v>370</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>3</v>
       </c>
       <c r="I4" t="b">
@@ -2622,7 +2918,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -2640,7 +2936,7 @@
       <c r="G5" t="s">
         <v>370</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>4</v>
       </c>
       <c r="I5" t="b">
@@ -2648,7 +2944,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -2666,7 +2962,7 @@
       <c r="G6" t="s">
         <v>370</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>5</v>
       </c>
       <c r="I6" t="b">
@@ -2674,7 +2970,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -2692,7 +2988,7 @@
       <c r="G7" t="s">
         <v>370</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>6</v>
       </c>
       <c r="I7" t="b">
@@ -2700,7 +2996,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -2721,7 +3017,7 @@
       <c r="G8" t="s">
         <v>370</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>7</v>
       </c>
       <c r="I8" t="b">
@@ -2729,7 +3025,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -2747,7 +3043,7 @@
       <c r="G9" t="s">
         <v>370</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>8</v>
       </c>
       <c r="I9" t="b">
@@ -2755,7 +3051,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -2773,7 +3069,7 @@
       <c r="G10" t="s">
         <v>370</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>9</v>
       </c>
       <c r="I10" t="b">
@@ -2781,7 +3077,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
@@ -2799,7 +3095,7 @@
       <c r="G11" t="s">
         <v>370</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>10</v>
       </c>
       <c r="I11" t="b">
@@ -2807,7 +3103,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
@@ -2825,7 +3121,7 @@
       <c r="G12" t="s">
         <v>370</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>11</v>
       </c>
       <c r="I12" t="b">
@@ -2833,7 +3129,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
@@ -2851,7 +3147,7 @@
       <c r="G13" t="s">
         <v>370</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>12</v>
       </c>
       <c r="I13" t="b">
@@ -2859,7 +3155,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
@@ -2877,7 +3173,7 @@
       <c r="G14" t="s">
         <v>370</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>13</v>
       </c>
       <c r="I14" t="b">
@@ -2885,7 +3181,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
@@ -2903,7 +3199,7 @@
       <c r="G15" t="s">
         <v>370</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>14</v>
       </c>
       <c r="I15" t="b">
@@ -2911,7 +3207,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
@@ -2929,7 +3225,7 @@
       <c r="G16" t="s">
         <v>370</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>15</v>
       </c>
       <c r="I16" t="b">
@@ -2937,7 +3233,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
@@ -2955,7 +3251,7 @@
       <c r="G17" t="s">
         <v>370</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>16</v>
       </c>
       <c r="I17" t="b">
@@ -2963,7 +3259,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
@@ -2981,7 +3277,7 @@
       <c r="G18" t="s">
         <v>370</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>17</v>
       </c>
       <c r="I18" t="b">
@@ -2989,7 +3285,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
@@ -3007,7 +3303,7 @@
       <c r="G19" t="s">
         <v>370</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>18</v>
       </c>
       <c r="I19" t="b">
@@ -3015,7 +3311,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
@@ -3033,7 +3329,7 @@
       <c r="G20" t="s">
         <v>370</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>19</v>
       </c>
       <c r="I20" t="b">
@@ -3041,7 +3337,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
@@ -3059,7 +3355,7 @@
       <c r="G21" t="s">
         <v>370</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>20</v>
       </c>
       <c r="I21" t="b">
@@ -3067,7 +3363,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
@@ -3085,7 +3381,7 @@
       <c r="G22" t="s">
         <v>370</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>21</v>
       </c>
       <c r="I22" t="b">
@@ -3093,7 +3389,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
@@ -3111,7 +3407,7 @@
       <c r="G23" t="s">
         <v>370</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>22</v>
       </c>
       <c r="I23" t="b">
@@ -3119,7 +3415,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
@@ -3137,7 +3433,7 @@
       <c r="G24" t="s">
         <v>370</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>23</v>
       </c>
       <c r="I24" t="b">
@@ -3145,7 +3441,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
@@ -3163,7 +3459,7 @@
       <c r="G25" t="s">
         <v>370</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>24</v>
       </c>
       <c r="I25" t="b">
@@ -3171,7 +3467,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
@@ -3189,7 +3485,7 @@
       <c r="G26" t="s">
         <v>370</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>25</v>
       </c>
       <c r="I26" t="b">
@@ -3197,7 +3493,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
@@ -3215,7 +3511,7 @@
       <c r="G27" t="s">
         <v>370</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>26</v>
       </c>
       <c r="I27" t="b">
@@ -3223,7 +3519,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
@@ -3241,7 +3537,7 @@
       <c r="G28" t="s">
         <v>370</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>27</v>
       </c>
       <c r="I28" t="b">
@@ -3249,7 +3545,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
@@ -3267,7 +3563,7 @@
       <c r="G29" t="s">
         <v>370</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>28</v>
       </c>
       <c r="I29" t="b">
@@ -3275,7 +3571,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
@@ -3293,7 +3589,7 @@
       <c r="G30" t="s">
         <v>370</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>29</v>
       </c>
       <c r="I30" t="b">
@@ -3301,7 +3597,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
@@ -3319,7 +3615,7 @@
       <c r="G31" t="s">
         <v>370</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>30</v>
       </c>
       <c r="I31" t="b">
@@ -3327,7 +3623,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
@@ -3345,7 +3641,7 @@
       <c r="G32" t="s">
         <v>370</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32">
         <v>31</v>
       </c>
       <c r="I32" t="b">
@@ -3353,21 +3649,22 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="38.88671875" hidden="0" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="38.88671875"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3378,64 +3675,73 @@
         <v>440</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C2" t="s">
         <v>443</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>444</v>
+      </c>
       <c r="D2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E2" t="s">
-        <v>445</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="b">
+        <v>446</v>
+      </c>
+      <c r="F2" t="s">
+        <v>447</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
-      <c r="C3" t="s">
-        <v>447</v>
+      <c r="C3" s="3" t="s">
+        <v>444</v>
       </c>
       <c r="D3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E3" t="s">
-        <v>449</v>
-      </c>
-      <c r="F3" t="n">
+        <v>450</v>
+      </c>
+      <c r="F3" t="s">
+        <v>451</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
-      <c r="G3" t="b">
+      <c r="H3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3446,365 +3752,411 @@
       <c r="B4" t="s">
         <v>65</v>
       </c>
-      <c r="C4" t="s">
-        <v>447</v>
+      <c r="C4" s="3" t="s">
+        <v>444</v>
       </c>
       <c r="D4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E4" t="s">
-        <v>449</v>
-      </c>
-      <c r="F4" t="n">
+        <v>450</v>
+      </c>
+      <c r="F4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G4">
         <v>3</v>
       </c>
-      <c r="G4" t="b">
+      <c r="H4" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B5" t="s">
         <v>84</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="D5" t="s">
+        <v>453</v>
+      </c>
+      <c r="E5" t="s">
+        <v>446</v>
+      </c>
+      <c r="F5" t="s">
         <v>451</v>
       </c>
-      <c r="D5" t="s">
-        <v>444</v>
-      </c>
-      <c r="E5" t="s">
-        <v>449</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="G5">
         <v>4</v>
       </c>
-      <c r="G5" t="b">
+      <c r="H5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B6" t="s">
         <v>87</v>
       </c>
-      <c r="C6" t="s">
-        <v>453</v>
+      <c r="C6" s="3" t="s">
+        <v>444</v>
       </c>
       <c r="D6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E6" t="s">
-        <v>449</v>
-      </c>
-      <c r="F6" t="n">
+        <v>456</v>
+      </c>
+      <c r="F6" t="s">
+        <v>451</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
-      <c r="G6" t="b">
+      <c r="H6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B7" t="s">
         <v>87</v>
       </c>
-      <c r="C7" t="s">
-        <v>456</v>
+      <c r="C7" s="3" t="s">
+        <v>444</v>
       </c>
       <c r="D7" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E7" t="s">
-        <v>449</v>
-      </c>
-      <c r="F7" t="n">
+        <v>459</v>
+      </c>
+      <c r="F7" t="s">
+        <v>451</v>
+      </c>
+      <c r="G7">
         <v>6</v>
       </c>
-      <c r="G7" t="b">
+      <c r="H7" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B8" t="s">
         <v>87</v>
       </c>
-      <c r="C8" t="s">
-        <v>458</v>
+      <c r="C8" s="3" t="s">
+        <v>444</v>
       </c>
       <c r="D8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E8" t="s">
-        <v>449</v>
-      </c>
-      <c r="F8" t="n">
+        <v>461</v>
+      </c>
+      <c r="F8" t="s">
+        <v>451</v>
+      </c>
+      <c r="G8">
         <v>7</v>
       </c>
-      <c r="G8" t="b">
+      <c r="H8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B9" t="s">
         <v>87</v>
       </c>
-      <c r="C9" t="s">
-        <v>460</v>
+      <c r="C9" s="3" t="s">
+        <v>444</v>
       </c>
       <c r="D9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E9" t="s">
-        <v>449</v>
-      </c>
-      <c r="F9" t="n">
+        <v>463</v>
+      </c>
+      <c r="F9" t="s">
+        <v>451</v>
+      </c>
+      <c r="G9">
         <v>8</v>
       </c>
-      <c r="G9" t="b">
+      <c r="H9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B10" t="s">
         <v>87</v>
       </c>
-      <c r="C10" t="s">
-        <v>460</v>
+      <c r="C10" s="3" t="s">
+        <v>444</v>
       </c>
       <c r="D10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E10" t="s">
-        <v>449</v>
-      </c>
-      <c r="F10" t="n">
+        <v>463</v>
+      </c>
+      <c r="F10" t="s">
+        <v>451</v>
+      </c>
+      <c r="G10">
         <v>9</v>
       </c>
-      <c r="G10" t="b">
+      <c r="H10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B11" t="s">
         <v>87</v>
       </c>
-      <c r="C11" t="s">
-        <v>463</v>
+      <c r="C11" s="3" t="s">
+        <v>444</v>
       </c>
       <c r="D11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E11" t="s">
-        <v>449</v>
-      </c>
-      <c r="F11" t="n">
+        <v>466</v>
+      </c>
+      <c r="F11" t="s">
+        <v>451</v>
+      </c>
+      <c r="G11">
         <v>10</v>
       </c>
-      <c r="G11" t="b">
+      <c r="H11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B12" t="s">
-        <v>466</v>
-      </c>
-      <c r="C12" t="s">
-        <v>467</v>
+        <v>468</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>469</v>
       </c>
       <c r="D12" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="E12" t="s">
-        <v>468</v>
-      </c>
-      <c r="F12" t="n">
+        <v>446</v>
+      </c>
+      <c r="F12" t="s">
+        <v>471</v>
+      </c>
+      <c r="G12">
         <v>11</v>
       </c>
-      <c r="G12" t="b">
+      <c r="H12" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>472</v>
+      </c>
+      <c r="B13" t="s">
+        <v>468</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="B13" t="s">
-        <v>466</v>
-      </c>
-      <c r="C13" t="s">
-        <v>470</v>
-      </c>
       <c r="D13" t="s">
+        <v>473</v>
+      </c>
+      <c r="E13" t="s">
+        <v>474</v>
+      </c>
+      <c r="F13" t="s">
         <v>471</v>
       </c>
-      <c r="E13" t="s">
-        <v>468</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="G13">
         <v>12</v>
       </c>
-      <c r="G13" t="b">
+      <c r="H13" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B14" t="s">
-        <v>466</v>
-      </c>
-      <c r="C14" t="s">
-        <v>470</v>
+        <v>468</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>469</v>
       </c>
       <c r="D14" t="s">
+        <v>473</v>
+      </c>
+      <c r="E14" t="s">
+        <v>474</v>
+      </c>
+      <c r="F14" t="s">
         <v>471</v>
       </c>
-      <c r="E14" t="s">
-        <v>468</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="G14">
         <v>13</v>
       </c>
-      <c r="G14" t="b">
+      <c r="H14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B15" t="s">
         <v>334</v>
       </c>
-      <c r="C15" t="s">
-        <v>473</v>
+      <c r="C15" s="3" t="s">
+        <v>469</v>
       </c>
       <c r="D15" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E15" t="s">
-        <v>468</v>
-      </c>
-      <c r="F15" t="n">
+        <v>477</v>
+      </c>
+      <c r="F15" t="s">
+        <v>471</v>
+      </c>
+      <c r="G15">
         <v>14</v>
       </c>
-      <c r="G15" t="b">
+      <c r="H15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B16" t="s">
-        <v>476</v>
-      </c>
-      <c r="C16" t="s">
-        <v>463</v>
+        <v>479</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>469</v>
       </c>
       <c r="D16" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E16" t="s">
-        <v>468</v>
-      </c>
-      <c r="F16" t="n">
+        <v>466</v>
+      </c>
+      <c r="F16" t="s">
+        <v>471</v>
+      </c>
+      <c r="G16">
         <v>15</v>
       </c>
-      <c r="G16" t="b">
+      <c r="H16" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>480</v>
+      </c>
+      <c r="B17" t="s">
+        <v>481</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D17" t="s">
+        <v>482</v>
+      </c>
+      <c r="E17" t="s">
         <v>477</v>
       </c>
-      <c r="B17" t="s">
-        <v>478</v>
-      </c>
-      <c r="C17" t="s">
-        <v>479</v>
-      </c>
-      <c r="D17" t="s">
-        <v>474</v>
-      </c>
-      <c r="E17" t="s">
-        <v>468</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="F17" t="s">
+        <v>471</v>
+      </c>
+      <c r="G17">
         <v>16</v>
       </c>
-      <c r="G17" t="b">
+      <c r="H17" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B18" t="s">
-        <v>481</v>
-      </c>
-      <c r="C18" t="s">
-        <v>482</v>
+        <v>484</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>469</v>
       </c>
       <c r="D18" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="E18" t="s">
-        <v>468</v>
-      </c>
-      <c r="F18" t="n">
+        <v>477</v>
+      </c>
+      <c r="F18" t="s">
+        <v>471</v>
+      </c>
+      <c r="G18">
         <v>17</v>
       </c>
-      <c r="G18" t="b">
+      <c r="H18" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>340</v>
@@ -3813,7 +4165,7 @@
         <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>38</v>
@@ -3824,18 +4176,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C2" t="s">
-        <v>488</v>
-      </c>
-      <c r="D2" t="n">
+        <v>491</v>
+      </c>
+      <c r="D2">
         <v>2009</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="b">
@@ -3844,18 +4196,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C3" t="s">
-        <v>490</v>
-      </c>
-      <c r="D3" t="n">
+        <v>493</v>
+      </c>
+      <c r="D3">
         <v>2008</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>2</v>
       </c>
       <c r="G3" t="b">
@@ -3864,15 +4216,15 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B4" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C4" t="s">
-        <v>492</v>
-      </c>
-      <c r="F4" t="n">
+        <v>495</v>
+      </c>
+      <c r="F4">
         <v>3</v>
       </c>
       <c r="G4" t="b">
@@ -3881,15 +4233,15 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B5" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C5" t="s">
-        <v>493</v>
-      </c>
-      <c r="F5" t="n">
+        <v>496</v>
+      </c>
+      <c r="F5">
         <v>4</v>
       </c>
       <c r="G5" t="b">
@@ -3898,15 +4250,15 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C6" t="s">
-        <v>494</v>
-      </c>
-      <c r="F6" t="n">
+        <v>497</v>
+      </c>
+      <c r="F6">
         <v>5</v>
       </c>
       <c r="G6" t="b">
@@ -3915,15 +4267,15 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B7" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C7" t="s">
-        <v>496</v>
-      </c>
-      <c r="F7" t="n">
+        <v>499</v>
+      </c>
+      <c r="F7">
         <v>6</v>
       </c>
       <c r="G7" t="b">
@@ -3932,15 +4284,15 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B8" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C8" t="s">
-        <v>497</v>
-      </c>
-      <c r="F8" t="n">
+        <v>500</v>
+      </c>
+      <c r="F8">
         <v>7</v>
       </c>
       <c r="G8" t="b">
@@ -3949,15 +4301,15 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B9" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C9" t="s">
-        <v>498</v>
-      </c>
-      <c r="F9" t="n">
+        <v>501</v>
+      </c>
+      <c r="F9">
         <v>8</v>
       </c>
       <c r="G9" t="b">
@@ -3966,15 +4318,15 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B10" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C10" t="s">
-        <v>500</v>
-      </c>
-      <c r="F10" t="n">
+        <v>503</v>
+      </c>
+      <c r="F10">
         <v>9</v>
       </c>
       <c r="G10" t="b">
@@ -3983,15 +4335,15 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B11" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C11" t="s">
-        <v>501</v>
-      </c>
-      <c r="F11" t="n">
+        <v>504</v>
+      </c>
+      <c r="F11">
         <v>10</v>
       </c>
       <c r="G11" t="b">
@@ -4000,15 +4352,15 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B12" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C12" t="s">
-        <v>502</v>
-      </c>
-      <c r="F12" t="n">
+        <v>505</v>
+      </c>
+      <c r="F12">
         <v>11</v>
       </c>
       <c r="G12" t="b">
@@ -4017,15 +4369,15 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B13" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C13" t="s">
-        <v>504</v>
-      </c>
-      <c r="F13" t="n">
+        <v>507</v>
+      </c>
+      <c r="F13">
         <v>12</v>
       </c>
       <c r="G13" t="b">
@@ -4034,15 +4386,15 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B14" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C14" t="s">
-        <v>505</v>
-      </c>
-      <c r="F14" t="n">
+        <v>508</v>
+      </c>
+      <c r="F14">
         <v>13</v>
       </c>
       <c r="G14" t="b">
@@ -4051,15 +4403,15 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B15" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C15" t="s">
-        <v>506</v>
-      </c>
-      <c r="F15" t="n">
+        <v>509</v>
+      </c>
+      <c r="F15">
         <v>14</v>
       </c>
       <c r="G15" t="b">
@@ -4067,23 +4419,24 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>29</v>
@@ -4098,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>38</v>
@@ -4109,18 +4462,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D2" t="s">
-        <v>511</v>
-      </c>
-      <c r="G2" t="n">
+        <v>514</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="b">
@@ -4129,21 +4482,21 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D3" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E3" t="s">
-        <v>514</v>
-      </c>
-      <c r="G3" t="n">
+        <v>517</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
       <c r="H3" t="b">
@@ -4152,18 +4505,18 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D4" t="s">
-        <v>447</v>
-      </c>
-      <c r="G4" t="n">
+        <v>449</v>
+      </c>
+      <c r="G4">
         <v>3</v>
       </c>
       <c r="H4" t="b">
@@ -4172,18 +4525,18 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D5" t="s">
-        <v>447</v>
-      </c>
-      <c r="G5" t="n">
+        <v>449</v>
+      </c>
+      <c r="G5">
         <v>4</v>
       </c>
       <c r="H5" t="b">
@@ -4192,21 +4545,21 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B6" t="s">
         <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E6" t="s">
-        <v>444</v>
-      </c>
-      <c r="G6" t="n">
+        <v>446</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
       <c r="H6" t="b">
@@ -4215,21 +4568,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B7" t="s">
         <v>239</v>
       </c>
       <c r="C7" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D7" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E7" t="s">
-        <v>521</v>
-      </c>
-      <c r="G7" t="n">
+        <v>524</v>
+      </c>
+      <c r="G7">
         <v>6</v>
       </c>
       <c r="H7" t="b">
@@ -4238,21 +4591,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B8" t="s">
         <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E8" t="s">
-        <v>522</v>
-      </c>
-      <c r="G8" t="n">
+        <v>525</v>
+      </c>
+      <c r="G8">
         <v>7</v>
       </c>
       <c r="H8" t="b">
@@ -4261,21 +4614,21 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B9" t="s">
         <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D9" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E9" t="s">
-        <v>524</v>
-      </c>
-      <c r="G9" t="n">
+        <v>527</v>
+      </c>
+      <c r="G9">
         <v>8</v>
       </c>
       <c r="H9" t="b">
@@ -4284,21 +4637,21 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B10" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C10" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E10" t="s">
-        <v>459</v>
-      </c>
-      <c r="G10" t="n">
+        <v>461</v>
+      </c>
+      <c r="G10">
         <v>9</v>
       </c>
       <c r="H10" t="b">
@@ -4307,21 +4660,21 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B11" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C11" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D11" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E11" t="s">
-        <v>528</v>
-      </c>
-      <c r="G11" t="n">
+        <v>531</v>
+      </c>
+      <c r="G11">
         <v>10</v>
       </c>
       <c r="H11" t="b">
@@ -4330,21 +4683,21 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B12" t="s">
         <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D12" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E12" t="s">
-        <v>522</v>
-      </c>
-      <c r="G12" t="n">
+        <v>525</v>
+      </c>
+      <c r="G12">
         <v>11</v>
       </c>
       <c r="H12" t="b">
@@ -4353,21 +4706,21 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B13" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C13" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D13" t="s">
+        <v>465</v>
+      </c>
+      <c r="E13" t="s">
         <v>463</v>
       </c>
-      <c r="E13" t="s">
-        <v>461</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>12</v>
       </c>
       <c r="H13" t="b">
@@ -4376,21 +4729,21 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B14" t="s">
         <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D14" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E14" t="s">
-        <v>534</v>
-      </c>
-      <c r="G14" t="n">
+        <v>537</v>
+      </c>
+      <c r="G14">
         <v>13</v>
       </c>
       <c r="H14" t="b">
@@ -4398,32 +4751,33 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>94</v>
@@ -4436,390 +4790,392 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E2" t="s">
         <v>111</v>
       </c>
       <c r="F2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C3" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D3" t="s">
         <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F3" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C4" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D4" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E4" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F4" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C5" t="s">
+        <v>554</v>
+      </c>
+      <c r="D5" t="s">
+        <v>542</v>
+      </c>
+      <c r="E5" t="s">
         <v>551</v>
       </c>
-      <c r="D5" t="s">
-        <v>539</v>
-      </c>
-      <c r="E5" t="s">
-        <v>548</v>
-      </c>
       <c r="F5" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C6" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D6" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E6" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F6" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C7" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D7" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E7" t="s">
         <v>119</v>
       </c>
       <c r="F7" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C8" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D8" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E8" t="s">
         <v>119</v>
       </c>
       <c r="F8" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C9" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D9" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E9" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F9" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C10" t="s">
         <v>381</v>
       </c>
       <c r="D10" t="s">
+        <v>573</v>
+      </c>
+      <c r="E10" t="s">
         <v>570</v>
       </c>
-      <c r="E10" t="s">
-        <v>567</v>
-      </c>
       <c r="F10" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C11" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D11" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="E11" t="s">
         <v>165</v>
       </c>
       <c r="F11" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C12" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D12" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E12" t="s">
         <v>175</v>
       </c>
       <c r="F12" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C13" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D13" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E13" t="s">
         <v>183</v>
       </c>
       <c r="F13" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C3" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D3" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E3" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B4" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C4" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D4" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E4" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E5" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B6" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C6" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D6" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E6" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B2" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -4827,10 +5183,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B3" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -4838,7 +5194,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -4849,10 +5205,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B5" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
@@ -4860,10 +5216,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B6" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -4871,10 +5227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B7" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -4882,10 +5238,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B8" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
@@ -4893,10 +5249,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B9" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -4904,10 +5260,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B10" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -4915,29 +5271,30 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B11" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -5017,19 +5374,20 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -5085,10 +5443,10 @@
       <c r="D2" t="s">
         <v>44</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>1991</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>1995</v>
       </c>
       <c r="G2" t="s">
@@ -5100,7 +5458,7 @@
       <c r="I2" t="s">
         <v>47</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>1</v>
       </c>
       <c r="L2" t="b">
@@ -5120,10 +5478,10 @@
       <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>1988</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>1991</v>
       </c>
       <c r="G3" t="s">
@@ -5132,7 +5490,7 @@
       <c r="H3" t="s">
         <v>53</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>2</v>
       </c>
       <c r="L3" t="b">
@@ -5152,10 +5510,10 @@
       <c r="D4" t="s">
         <v>44</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>1981</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>1985</v>
       </c>
       <c r="G4" t="s">
@@ -5164,7 +5522,7 @@
       <c r="H4" t="s">
         <v>56</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>3</v>
       </c>
       <c r="L4" t="b">
@@ -5172,23 +5530,24 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.5546875" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="56.109375" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" hidden="0" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="21.5546875"/>
+    <col customWidth="1" min="2" max="2" width="56.109375"/>
+    <col customWidth="1" min="3" max="3" width="19.6640625"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5239,13 +5598,13 @@
       <c r="C2" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2">
         <v>44197</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2">
         <v>45869</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="s">
@@ -5265,13 +5624,13 @@
       <c r="C3" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="2">
         <v>44197</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="2">
         <v>45869</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>2</v>
       </c>
       <c r="J3" t="s">
@@ -5291,13 +5650,13 @@
       <c r="C4" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2">
         <v>44197</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="2">
         <v>45869</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>3</v>
       </c>
       <c r="J4" t="s">
@@ -5317,13 +5676,13 @@
       <c r="C5" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="2">
         <v>44197</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="2">
         <v>45869</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>4</v>
       </c>
       <c r="J5" t="s">
@@ -5343,13 +5702,13 @@
       <c r="C6" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="2">
         <v>44197</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="2">
         <v>45869</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>5</v>
       </c>
       <c r="J6" t="s">
@@ -5369,13 +5728,13 @@
       <c r="C7" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="2">
         <v>44197</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="2">
         <v>45869</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>6</v>
       </c>
       <c r="J7" t="s">
@@ -5395,13 +5754,13 @@
       <c r="C8" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="2">
         <v>44197</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="2">
         <v>45869</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>7</v>
       </c>
       <c r="J8" t="s">
@@ -5421,13 +5780,13 @@
       <c r="C9" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="2">
         <v>44197</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="2">
         <v>45869</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>8</v>
       </c>
       <c r="J9" t="s">
@@ -5447,13 +5806,13 @@
       <c r="C10" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="2">
         <v>44197</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="2">
         <v>45869</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>9</v>
       </c>
       <c r="J10" t="s">
@@ -5473,13 +5832,13 @@
       <c r="C11" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="2">
         <v>44197</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="2">
         <v>45869</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>10</v>
       </c>
       <c r="J11" t="s">
@@ -5499,13 +5858,13 @@
       <c r="C12" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="2">
         <v>44197</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="2">
         <v>45869</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>11</v>
       </c>
       <c r="J12" t="s">
@@ -5525,13 +5884,13 @@
       <c r="C13" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="2">
         <v>44197</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="2">
         <v>45869</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>12</v>
       </c>
       <c r="J13" t="s">
@@ -5551,13 +5910,13 @@
       <c r="C14" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="2">
         <v>44197</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="2">
         <v>45869</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>13</v>
       </c>
       <c r="J14" t="s">
@@ -5577,13 +5936,13 @@
       <c r="C15" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="2">
         <v>44197</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="2">
         <v>45869</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>14</v>
       </c>
       <c r="J15" t="s">
@@ -5603,13 +5962,13 @@
       <c r="C16" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="2">
         <v>43466</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="2">
         <v>44166</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>15</v>
       </c>
       <c r="J16" t="s">
@@ -5629,13 +5988,13 @@
       <c r="C17" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="2">
         <v>37803</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="2">
         <v>43282</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>16</v>
       </c>
       <c r="J17" t="s">
@@ -5655,13 +6014,13 @@
       <c r="C18" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="2">
         <v>37803</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="2">
         <v>43282</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>17</v>
       </c>
       <c r="J18" t="s">
@@ -5672,19 +6031,20 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -5731,7 +6091,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -5749,7 +6109,7 @@
       <c r="I2" t="s">
         <v>107</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="b">
@@ -5757,7 +6117,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -5772,7 +6132,7 @@
       <c r="E3" t="s">
         <v>111</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="b">
@@ -5780,7 +6140,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -5795,7 +6155,7 @@
       <c r="E4" t="s">
         <v>115</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="b">
@@ -5803,7 +6163,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -5821,7 +6181,7 @@
       <c r="I5" t="s">
         <v>120</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="b">
@@ -5829,7 +6189,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -5847,7 +6207,7 @@
       <c r="I6" t="s">
         <v>125</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="b">
@@ -5855,7 +6215,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -5873,7 +6233,7 @@
       <c r="I7" t="s">
         <v>130</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="b">
@@ -5881,7 +6241,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -5899,7 +6259,7 @@
       <c r="I8" t="s">
         <v>134</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="b">
@@ -5907,7 +6267,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -5925,7 +6285,7 @@
       <c r="I9" t="s">
         <v>139</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="b">
@@ -5933,7 +6293,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -5951,7 +6311,7 @@
       <c r="I10" t="s">
         <v>143</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="b">
@@ -5959,7 +6319,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
@@ -5977,7 +6337,7 @@
       <c r="I11" t="s">
         <v>148</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="b">
@@ -5985,7 +6345,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
@@ -6003,7 +6363,7 @@
       <c r="I12" t="s">
         <v>153</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="b">
@@ -6011,7 +6371,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
@@ -6026,7 +6386,7 @@
       <c r="E13" t="s">
         <v>157</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="b">
@@ -6034,7 +6394,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
@@ -6049,7 +6409,7 @@
       <c r="E14" t="s">
         <v>161</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="b">
@@ -6057,7 +6417,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
@@ -6075,7 +6435,7 @@
       <c r="I15" t="s">
         <v>166</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="b">
@@ -6083,7 +6443,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
@@ -6101,7 +6461,7 @@
       <c r="I16" t="s">
         <v>171</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="b">
@@ -6109,7 +6469,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
@@ -6127,7 +6487,7 @@
       <c r="I17" t="s">
         <v>176</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>0</v>
       </c>
       <c r="M17" t="b">
@@ -6135,7 +6495,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
@@ -6153,7 +6513,7 @@
       <c r="I18" t="s">
         <v>180</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="b">
@@ -6161,7 +6521,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
@@ -6179,7 +6539,7 @@
       <c r="I19" t="s">
         <v>184</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>0</v>
       </c>
       <c r="M19" t="b">
@@ -6187,7 +6547,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
@@ -6205,7 +6565,7 @@
       <c r="I20" t="s">
         <v>187</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="b">
@@ -6213,7 +6573,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
@@ -6231,7 +6591,7 @@
       <c r="I21" t="s">
         <v>190</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="b">
@@ -6239,7 +6599,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
@@ -6257,7 +6617,7 @@
       <c r="I22" t="s">
         <v>194</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="b">
@@ -6265,7 +6625,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
@@ -6283,7 +6643,7 @@
       <c r="I23" t="s">
         <v>198</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="b">
@@ -6291,19 +6651,20 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -6344,7 +6705,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -6356,7 +6717,7 @@
       <c r="D2" t="s">
         <v>206</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>1</v>
       </c>
       <c r="K2" t="b">
@@ -6364,7 +6725,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -6376,7 +6737,7 @@
       <c r="D3" t="s">
         <v>208</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>2</v>
       </c>
       <c r="K3" t="b">
@@ -6384,7 +6745,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -6396,7 +6757,7 @@
       <c r="D4" t="s">
         <v>211</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>3</v>
       </c>
       <c r="K4" t="b">
@@ -6404,19 +6765,20 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -6466,7 +6828,7 @@
       <c r="G2" t="s">
         <v>220</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="b">
@@ -6489,7 +6851,7 @@
       <c r="G3" t="s">
         <v>221</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>2</v>
       </c>
       <c r="J3" t="b">
@@ -6515,7 +6877,7 @@
       <c r="G4" t="s">
         <v>226</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>3</v>
       </c>
       <c r="J4" t="b">
@@ -6541,7 +6903,7 @@
       <c r="G5" t="s">
         <v>227</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>4</v>
       </c>
       <c r="J5" t="b">
@@ -6567,7 +6929,7 @@
       <c r="G6" t="s">
         <v>228</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>5</v>
       </c>
       <c r="J6" t="b">
@@ -6593,7 +6955,7 @@
       <c r="G7" t="s">
         <v>229</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>6</v>
       </c>
       <c r="J7" t="b">
@@ -6619,7 +6981,7 @@
       <c r="G8" t="s">
         <v>234</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>7</v>
       </c>
       <c r="J8" t="b">
@@ -6645,7 +7007,7 @@
       <c r="G9" t="s">
         <v>235</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>8</v>
       </c>
       <c r="J9" t="b">
@@ -6671,7 +7033,7 @@
       <c r="G10" t="s">
         <v>236</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>9</v>
       </c>
       <c r="J10" t="b">
@@ -6697,7 +7059,7 @@
       <c r="G11" t="s">
         <v>237</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>10</v>
       </c>
       <c r="J11" t="b">
@@ -6723,7 +7085,7 @@
       <c r="G12" t="s">
         <v>238</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>11</v>
       </c>
       <c r="J12" t="b">
@@ -6749,7 +7111,7 @@
       <c r="G13" t="s">
         <v>244</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>12</v>
       </c>
       <c r="J13" t="b">
@@ -6775,7 +7137,7 @@
       <c r="G14" t="s">
         <v>245</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>13</v>
       </c>
       <c r="J14" t="b">
@@ -6801,7 +7163,7 @@
       <c r="G15" t="s">
         <v>246</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>14</v>
       </c>
       <c r="J15" t="b">
@@ -6827,7 +7189,7 @@
       <c r="G16" t="s">
         <v>247</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>15</v>
       </c>
       <c r="J16" t="b">
@@ -6850,7 +7212,7 @@
       <c r="G17" t="s">
         <v>251</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>16</v>
       </c>
       <c r="J17" t="b">
@@ -6873,7 +7235,7 @@
       <c r="G18" t="s">
         <v>252</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>17</v>
       </c>
       <c r="J18" t="b">
@@ -6896,7 +7258,7 @@
       <c r="G19" t="s">
         <v>253</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>18</v>
       </c>
       <c r="J19" t="b">
@@ -6919,7 +7281,7 @@
       <c r="G20" t="s">
         <v>254</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>19</v>
       </c>
       <c r="J20" t="b">
@@ -6942,7 +7304,7 @@
       <c r="G21" t="s">
         <v>255</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>20</v>
       </c>
       <c r="J21" t="b">
@@ -6968,7 +7330,7 @@
       <c r="G22" t="s">
         <v>261</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>21</v>
       </c>
       <c r="J22" t="b">
@@ -6994,7 +7356,7 @@
       <c r="G23" t="s">
         <v>266</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>22</v>
       </c>
       <c r="J23" t="b">
@@ -7020,7 +7382,7 @@
       <c r="G24" t="s">
         <v>267</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>23</v>
       </c>
       <c r="J24" t="b">
@@ -7046,7 +7408,7 @@
       <c r="G25" t="s">
         <v>271</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>24</v>
       </c>
       <c r="J25" t="b">
@@ -7072,7 +7434,7 @@
       <c r="G26" t="s">
         <v>272</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>25</v>
       </c>
       <c r="J26" t="b">
@@ -7098,7 +7460,7 @@
       <c r="G27" t="s">
         <v>275</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>26</v>
       </c>
       <c r="J27" t="b">
@@ -7106,21 +7468,22 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="86.5546875" hidden="0" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="86.5546875"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7162,13 +7525,13 @@
       <c r="C2" t="s">
         <v>282</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>2024</v>
       </c>
       <c r="F2" t="s">
         <v>283</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="b">
@@ -7185,13 +7548,13 @@
       <c r="C3" t="s">
         <v>282</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>2023</v>
       </c>
       <c r="F3" t="s">
         <v>283</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>2</v>
       </c>
       <c r="H3" t="b">
@@ -7208,13 +7571,13 @@
       <c r="C4" t="s">
         <v>282</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>2023</v>
       </c>
       <c r="F4" t="s">
         <v>283</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>3</v>
       </c>
       <c r="H4" t="b">
@@ -7231,13 +7594,13 @@
       <c r="C5" t="s">
         <v>282</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>2022</v>
       </c>
       <c r="F5" t="s">
         <v>285</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>4</v>
       </c>
       <c r="H5" t="b">
@@ -7254,13 +7617,13 @@
       <c r="C6" t="s">
         <v>287</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>2020</v>
       </c>
       <c r="F6" t="s">
         <v>288</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>5</v>
       </c>
       <c r="H6" t="b">
@@ -7277,13 +7640,13 @@
       <c r="C7" t="s">
         <v>290</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>2017</v>
       </c>
       <c r="F7" t="s">
         <v>283</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>6</v>
       </c>
       <c r="H7" t="b">
@@ -7300,13 +7663,13 @@
       <c r="C8" t="s">
         <v>290</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>2016</v>
       </c>
       <c r="F8" t="s">
         <v>283</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>7</v>
       </c>
       <c r="H8" t="b">
@@ -7323,13 +7686,13 @@
       <c r="C9" t="s">
         <v>293</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>2016</v>
       </c>
       <c r="F9" t="s">
         <v>294</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>8</v>
       </c>
       <c r="H9" t="b">
@@ -7346,13 +7709,13 @@
       <c r="C10" t="s">
         <v>293</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>2014</v>
       </c>
       <c r="F10" t="s">
         <v>283</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>9</v>
       </c>
       <c r="H10" t="b">
@@ -7369,13 +7732,13 @@
       <c r="C11" t="s">
         <v>293</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>2013</v>
       </c>
       <c r="F11" t="s">
         <v>283</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>10</v>
       </c>
       <c r="H11" t="b">
@@ -7392,13 +7755,13 @@
       <c r="C12" t="s">
         <v>293</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>2012</v>
       </c>
       <c r="F12" t="s">
         <v>294</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>11</v>
       </c>
       <c r="H12" t="b">
@@ -7415,13 +7778,13 @@
       <c r="C13" t="s">
         <v>299</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>2005</v>
       </c>
       <c r="F13" t="s">
         <v>283</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>12</v>
       </c>
       <c r="H13" t="b">
@@ -7438,13 +7801,13 @@
       <c r="C14" t="s">
         <v>293</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>2003</v>
       </c>
       <c r="F14" t="s">
         <v>294</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>13</v>
       </c>
       <c r="H14" t="b">
@@ -7461,13 +7824,13 @@
       <c r="C15" t="s">
         <v>293</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>2002</v>
       </c>
       <c r="F15" t="s">
         <v>294</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>14</v>
       </c>
       <c r="H15" t="b">
@@ -7484,13 +7847,13 @@
       <c r="C16" t="s">
         <v>293</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>2001</v>
       </c>
       <c r="F16" t="s">
         <v>294</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>15</v>
       </c>
       <c r="H16" t="b">
@@ -7507,13 +7870,13 @@
       <c r="C17" t="s">
         <v>293</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>2000</v>
       </c>
       <c r="F17" t="s">
         <v>294</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>16</v>
       </c>
       <c r="H17" t="b">
@@ -7530,13 +7893,13 @@
       <c r="C18" t="s">
         <v>293</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>2000</v>
       </c>
       <c r="F18" t="s">
         <v>294</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>17</v>
       </c>
       <c r="H18" t="b">
@@ -7553,13 +7916,13 @@
       <c r="C19" t="s">
         <v>290</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>1999</v>
       </c>
       <c r="F19" t="s">
         <v>283</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>18</v>
       </c>
       <c r="H19" t="b">
@@ -7576,13 +7939,13 @@
       <c r="C20" t="s">
         <v>290</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>1998</v>
       </c>
       <c r="F20" t="s">
         <v>288</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>19</v>
       </c>
       <c r="H20" t="b">
@@ -7599,13 +7962,13 @@
       <c r="C21" t="s">
         <v>307</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>1997</v>
       </c>
       <c r="F21" t="s">
         <v>283</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>20</v>
       </c>
       <c r="H21" t="b">
@@ -7622,13 +7985,13 @@
       <c r="C22" t="s">
         <v>310</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>1997</v>
       </c>
       <c r="F22" t="s">
         <v>283</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>21</v>
       </c>
       <c r="H22" t="b">
@@ -7645,13 +8008,13 @@
       <c r="C23" t="s">
         <v>312</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>1996</v>
       </c>
       <c r="F23" t="s">
         <v>283</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>22</v>
       </c>
       <c r="H23" t="b">
@@ -7668,13 +8031,13 @@
       <c r="C24" t="s">
         <v>290</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>1995</v>
       </c>
       <c r="F24" t="s">
         <v>283</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>23</v>
       </c>
       <c r="H24" t="b">
@@ -7691,13 +8054,13 @@
       <c r="C25" t="s">
         <v>317</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>1994</v>
       </c>
       <c r="F25" t="s">
         <v>288</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>24</v>
       </c>
       <c r="H25" t="b">
@@ -7714,13 +8077,13 @@
       <c r="C26" t="s">
         <v>320</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>1994</v>
       </c>
       <c r="F26" t="s">
         <v>283</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>25</v>
       </c>
       <c r="H26" t="b">
@@ -7737,13 +8100,13 @@
       <c r="C27" t="s">
         <v>322</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>1991</v>
       </c>
       <c r="F27" t="s">
         <v>288</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>26</v>
       </c>
       <c r="H27" t="b">
@@ -7751,19 +8114,20 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -7801,13 +8165,13 @@
       <c r="B2" t="s">
         <v>328</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>2005</v>
       </c>
       <c r="E2" t="s">
         <v>329</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="b">
@@ -7824,13 +8188,13 @@
       <c r="B3" t="s">
         <v>332</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>2003</v>
       </c>
       <c r="E3" t="s">
         <v>329</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>2</v>
       </c>
       <c r="G3" t="b">
@@ -7847,13 +8211,13 @@
       <c r="B4" t="s">
         <v>335</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>1999</v>
       </c>
       <c r="E4" t="s">
         <v>329</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>3</v>
       </c>
       <c r="G4" t="b">
@@ -7870,13 +8234,13 @@
       <c r="B5" t="s">
         <v>338</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>1997</v>
       </c>
       <c r="E5" t="s">
         <v>329</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>4</v>
       </c>
       <c r="G5" t="b">
@@ -7887,7 +8251,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>